--- a/docs/pricelist/samsung-Mobiles.xlsx
+++ b/docs/pricelist/samsung-Mobiles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Pictures\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BADE706-CACC-4850-8C8F-6DFCE76DF6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDA1ADD-1850-4063-8470-BAAE2037E623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
   <si>
     <t>Model</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>12/128</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -126,9 +129,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,6 +452,12 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
@@ -454,6 +466,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
@@ -462,6 +480,9 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -473,6 +494,12 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
@@ -481,6 +508,9 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
@@ -492,6 +522,12 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
@@ -500,6 +536,9 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
@@ -511,6 +550,12 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
@@ -519,6 +564,12 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
@@ -527,6 +578,9 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
@@ -538,11 +592,31 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="1">
         <v>121500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
